--- a/가톨릭관동대학교-24학년도-정시.xlsx
+++ b/가톨릭관동대학교-24학년도-정시.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\findmyuniv data\findmyuniv_data_cleaning\"/>
@@ -26,14 +26,14 @@
     <sheet name="가톨릭관동대학교-24학년도-정시" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'가톨릭관동대학교-24학년도-정시'!$A$1:$DC$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'가톨릭관동대학교-24학년도-정시'!$A$1:$DC$28</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="359">
   <si>
     <t>비교대학 추가</t>
   </si>
@@ -1225,7 +1225,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1262,13 +1262,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1572,6 +1572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1593,6 +1594,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1864,6 +1866,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -2215,336 +2218,340 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DC29"/>
+  <sheetPr codeName="Sheet12"/>
+  <dimension ref="A1:DC28"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.796875" style="4"/>
-    <col min="5" max="5" width="18.296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="4"/>
+    <col min="1" max="1" width="15.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.796875" style="2"/>
+    <col min="5" max="5" width="18.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="57" width="8.796875" style="2"/>
+    <col min="58" max="59" width="10.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="8.796875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:107" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BT1" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BV1" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BW1" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BX1" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BY1" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="CA1" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="CB1" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CC1" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CD1" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CE1" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CF1" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CG1" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CI1" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CK1" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CL1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CM1" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CN1" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CO1" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CP1" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="CR1" s="2" t="s">
+      <c r="CR1" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CS1" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="CZ1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="DA1" s="2" t="s">
+      <c r="DA1" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="DC1" s="3" t="s">
+      <c r="DC1" s="4" t="s">
         <v>350</v>
       </c>
     </row>
@@ -4491,25 +4498,27 @@
         <v>351</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="H13" s="5"/>
+        <v>123</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>152</v>
+      </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="K13" s="5">
         <v>1000</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -4664,27 +4673,27 @@
         <v>351</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K14" s="5">
         <v>1000</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -4839,27 +4848,27 @@
         <v>351</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="K15" s="5">
         <v>1000</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -5014,27 +5023,27 @@
         <v>351</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>231</v>
+        <v>38</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>211</v>
+        <v>122</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>219</v>
+        <v>170</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
-        <v>232</v>
+        <v>172</v>
       </c>
       <c r="K16" s="5">
         <v>1000</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5" t="s">
-        <v>233</v>
+        <v>173</v>
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -5050,27 +5059,31 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
       <c r="AA16" s="5"/>
-      <c r="AB16" s="5"/>
+      <c r="AB16" s="5" t="s">
+        <v>357</v>
+      </c>
       <c r="AC16" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AD16" s="5"/>
-      <c r="AE16" s="5"/>
-      <c r="AF16" s="5"/>
+      <c r="AE16" s="5">
+        <v>20</v>
+      </c>
+      <c r="AF16" s="5">
+        <v>30</v>
+      </c>
       <c r="AG16" s="5">
         <v>20</v>
       </c>
       <c r="AH16" s="5"/>
-      <c r="AI16" s="5"/>
+      <c r="AI16" s="5">
+        <v>30</v>
+      </c>
       <c r="AJ16" s="5"/>
       <c r="AK16" s="5"/>
       <c r="AL16" s="5"/>
-      <c r="AM16" s="5">
-        <v>40</v>
-      </c>
-      <c r="AN16" s="5">
-        <v>40</v>
-      </c>
+      <c r="AM16" s="5"/>
+      <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
       <c r="AQ16" s="5"/>
@@ -5156,13 +5169,17 @@
       <c r="CI16" s="5"/>
       <c r="CJ16" s="5"/>
       <c r="CK16" s="5"/>
-      <c r="CL16" s="5"/>
+      <c r="CL16" s="5" t="s">
+        <v>357</v>
+      </c>
       <c r="CM16" s="5"/>
       <c r="CN16" s="5"/>
       <c r="CO16" s="5"/>
       <c r="CP16" s="5"/>
       <c r="CQ16" s="5"/>
-      <c r="CR16" s="5"/>
+      <c r="CR16" s="5">
+        <v>0.05</v>
+      </c>
       <c r="CS16" s="5"/>
       <c r="CT16" s="5"/>
       <c r="CU16" s="5"/>
@@ -5189,27 +5206,27 @@
         <v>351</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>38</v>
+        <v>178</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="K17" s="5">
         <v>1000</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
@@ -5225,31 +5242,27 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
       <c r="AA17" s="5"/>
-      <c r="AB17" s="5" t="s">
-        <v>357</v>
-      </c>
+      <c r="AB17" s="5"/>
       <c r="AC17" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AD17" s="5"/>
-      <c r="AE17" s="5">
-        <v>20</v>
-      </c>
-      <c r="AF17" s="5">
-        <v>30</v>
-      </c>
+      <c r="AE17" s="5"/>
+      <c r="AF17" s="5"/>
       <c r="AG17" s="5">
         <v>20</v>
       </c>
       <c r="AH17" s="5"/>
-      <c r="AI17" s="5">
-        <v>30</v>
-      </c>
+      <c r="AI17" s="5"/>
       <c r="AJ17" s="5"/>
       <c r="AK17" s="5"/>
       <c r="AL17" s="5"/>
-      <c r="AM17" s="5"/>
-      <c r="AN17" s="5"/>
+      <c r="AM17" s="5">
+        <v>40</v>
+      </c>
+      <c r="AN17" s="5">
+        <v>40</v>
+      </c>
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
       <c r="AQ17" s="5"/>
@@ -5335,17 +5348,13 @@
       <c r="CI17" s="5"/>
       <c r="CJ17" s="5"/>
       <c r="CK17" s="5"/>
-      <c r="CL17" s="5" t="s">
-        <v>357</v>
-      </c>
+      <c r="CL17" s="5"/>
       <c r="CM17" s="5"/>
       <c r="CN17" s="5"/>
       <c r="CO17" s="5"/>
       <c r="CP17" s="5"/>
       <c r="CQ17" s="5"/>
-      <c r="CR17" s="5">
-        <v>0.05</v>
-      </c>
+      <c r="CR17" s="5"/>
       <c r="CS17" s="5"/>
       <c r="CT17" s="5"/>
       <c r="CU17" s="5"/>
@@ -5372,27 +5381,27 @@
         <v>351</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="K18" s="5">
         <v>1000</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
@@ -5541,33 +5550,31 @@
         <v>352</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>351</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>217</v>
+        <v>142</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>220</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
-        <v>221</v>
+        <v>144</v>
       </c>
       <c r="K19" s="5">
         <v>1000</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5" t="s">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
@@ -5716,31 +5723,33 @@
         <v>352</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>351</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H20" s="5"/>
+        <v>123</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>195</v>
+      </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5" t="s">
-        <v>144</v>
+        <v>196</v>
       </c>
       <c r="K20" s="5">
         <v>1000</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
@@ -5895,27 +5904,27 @@
         <v>351</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="K21" s="5">
         <v>1000</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
@@ -6070,27 +6079,27 @@
         <v>351</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="K22" s="5">
         <v>1000</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
@@ -6245,27 +6254,27 @@
         <v>351</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>129</v>
+        <v>236</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="K23" s="5">
         <v>1000</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
@@ -6414,33 +6423,33 @@
         <v>352</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>351</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>234</v>
+        <v>146</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>235</v>
+        <v>122</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>236</v>
+        <v>147</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
-        <v>237</v>
+        <v>149</v>
       </c>
       <c r="K24" s="5">
         <v>1000</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5" t="s">
-        <v>238</v>
+        <v>150</v>
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
@@ -6589,33 +6598,33 @@
         <v>352</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>351</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>146</v>
+        <v>243</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="K25" s="5">
         <v>1000</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
@@ -6764,33 +6773,33 @@
         <v>352</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>351</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>243</v>
+        <v>164</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>244</v>
+        <v>135</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="K26" s="5">
         <v>1000</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5" t="s">
-        <v>246</v>
+        <v>168</v>
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
@@ -6945,27 +6954,27 @@
         <v>351</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="K27" s="5">
         <v>1000</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
@@ -7120,7 +7129,7 @@
         <v>351</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>128</v>
@@ -7129,18 +7138,18 @@
         <v>129</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K28" s="5">
         <v>1000</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
@@ -7281,181 +7290,6 @@
       <c r="DB28" s="5"/>
       <c r="DC28" s="5"/>
     </row>
-    <row r="29" spans="1:107" x14ac:dyDescent="0.4">
-      <c r="A29" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="K29" s="5">
-        <v>1000</v>
-      </c>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
-      <c r="V29" s="5"/>
-      <c r="W29" s="5"/>
-      <c r="X29" s="5"/>
-      <c r="Y29" s="5"/>
-      <c r="Z29" s="5"/>
-      <c r="AA29" s="5"/>
-      <c r="AB29" s="5"/>
-      <c r="AC29" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="AD29" s="5"/>
-      <c r="AE29" s="5"/>
-      <c r="AF29" s="5"/>
-      <c r="AG29" s="5">
-        <v>20</v>
-      </c>
-      <c r="AH29" s="5"/>
-      <c r="AI29" s="5"/>
-      <c r="AJ29" s="5"/>
-      <c r="AK29" s="5"/>
-      <c r="AL29" s="5"/>
-      <c r="AM29" s="5">
-        <v>40</v>
-      </c>
-      <c r="AN29" s="5">
-        <v>40</v>
-      </c>
-      <c r="AO29" s="5"/>
-      <c r="AP29" s="5"/>
-      <c r="AQ29" s="5"/>
-      <c r="AR29" s="5"/>
-      <c r="AS29" s="5"/>
-      <c r="AT29" s="5"/>
-      <c r="AU29" s="5"/>
-      <c r="AV29" s="5"/>
-      <c r="AW29" s="5"/>
-      <c r="AX29" s="5"/>
-      <c r="AY29" s="5"/>
-      <c r="AZ29" s="5"/>
-      <c r="BA29" s="5"/>
-      <c r="BB29" s="5"/>
-      <c r="BC29" s="5"/>
-      <c r="BD29" s="5"/>
-      <c r="BE29" s="5"/>
-      <c r="BF29" s="5"/>
-      <c r="BG29" s="5"/>
-      <c r="BH29" s="5"/>
-      <c r="BI29" s="5"/>
-      <c r="BJ29" s="5"/>
-      <c r="BK29" s="5">
-        <v>200</v>
-      </c>
-      <c r="BL29" s="5">
-        <v>192.5</v>
-      </c>
-      <c r="BM29" s="5">
-        <v>185</v>
-      </c>
-      <c r="BN29" s="5">
-        <v>177.5</v>
-      </c>
-      <c r="BO29" s="5">
-        <v>170</v>
-      </c>
-      <c r="BP29" s="5">
-        <v>162.5</v>
-      </c>
-      <c r="BQ29" s="5">
-        <v>155</v>
-      </c>
-      <c r="BR29" s="5">
-        <v>147.5</v>
-      </c>
-      <c r="BS29" s="5">
-        <v>140</v>
-      </c>
-      <c r="BT29" s="5">
-        <v>10</v>
-      </c>
-      <c r="BU29" s="5">
-        <v>10</v>
-      </c>
-      <c r="BV29" s="5">
-        <v>10</v>
-      </c>
-      <c r="BW29" s="5">
-        <v>10</v>
-      </c>
-      <c r="BX29" s="5">
-        <v>9.6</v>
-      </c>
-      <c r="BY29" s="5">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="BZ29" s="5">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="CA29" s="5">
-        <v>8.4</v>
-      </c>
-      <c r="CB29" s="5">
-        <v>8</v>
-      </c>
-      <c r="CC29" s="5"/>
-      <c r="CD29" s="5"/>
-      <c r="CE29" s="5"/>
-      <c r="CF29" s="5"/>
-      <c r="CG29" s="5"/>
-      <c r="CH29" s="5"/>
-      <c r="CI29" s="5"/>
-      <c r="CJ29" s="5"/>
-      <c r="CK29" s="5"/>
-      <c r="CL29" s="5"/>
-      <c r="CM29" s="5"/>
-      <c r="CN29" s="5"/>
-      <c r="CO29" s="5"/>
-      <c r="CP29" s="5"/>
-      <c r="CQ29" s="5"/>
-      <c r="CR29" s="5"/>
-      <c r="CS29" s="5"/>
-      <c r="CT29" s="5"/>
-      <c r="CU29" s="5"/>
-      <c r="CV29" s="5"/>
-      <c r="CW29" s="5"/>
-      <c r="CX29" s="5"/>
-      <c r="CY29" s="5"/>
-      <c r="CZ29" s="5"/>
-      <c r="DA29" s="5"/>
-      <c r="DB29" s="5"/>
-      <c r="DC29" s="5"/>
-    </row>
   </sheetData>
   <sortState ref="A2:DC29">
     <sortCondition ref="E2:E29"/>
@@ -7468,6 +7302,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -7500,6 +7335,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -7589,6 +7425,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -7610,6 +7447,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -7626,6 +7464,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -7725,6 +7564,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -7786,6 +7626,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -7968,6 +7809,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
